--- a/arsip/cba-1.xlsx
+++ b/arsip/cba-1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
             <charset val="0"/>
           </rPr>
           <t xml:space="preserve">
-biaya instalasi di awal</t>
+biaya instalasi/investasi di awal</t>
         </r>
       </text>
     </comment>
@@ -801,11 +801,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1390,19 +1393,19 @@
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="2"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>500000000</v>
       </c>
     </row>
@@ -1410,7 +1413,7 @@
       <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>0.2</v>
       </c>
     </row>
@@ -1418,7 +1421,7 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1426,7 +1429,7 @@
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -1434,7 +1437,7 @@
       <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1442,7 +1445,7 @@
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>60000000</v>
       </c>
     </row>
@@ -1450,15 +1453,15 @@
       <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>100000000</v>
       </c>
     </row>
     <row r="13" spans="3:3">
-      <c r="C13" s="8"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1466,7 +1469,7 @@
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <f>C7/C9</f>
         <v>0</v>
       </c>
@@ -1475,13 +1478,13 @@
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <f>+C15+C10</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1489,16 +1492,16 @@
       <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>C5*C8+C16</f>
         <v>85000000</v>
       </c>
     </row>
     <row r="21" spans="3:3">
-      <c r="C21" s="7"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1506,27 +1509,27 @@
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <f>C11-C20</f>
         <v>15000000</v>
       </c>
     </row>
     <row r="24" spans="3:3">
-      <c r="C24" s="7"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="9" t="str">
+      <c r="B26" s="10" t="str">
         <f>IF(C23&gt;=0,"👍 benefit&gt;cost, tindakan mitigasi layak direkomendasikan","👎 benefit &lt; cost, tindakan mitigasi tidak direkomendasikan")</f>
         <v>👍 benefit&gt;cost, tindakan mitigasi layak direkomendasikan</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/arsip/cba-1.xlsx
+++ b/arsip/cba-1.xlsx
@@ -1454,6 +1454,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="8">
+        <f>C5*C6</f>
         <v>100000000</v>
       </c>
     </row>
